--- a/relatorio_registros.xlsx
+++ b/relatorio_registros.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50 MG/ML SOL INJ IV CX 10 BOLS PLAS SIST FECH X 1000 ML Ativo</t>
+          <t>50 MG/ML SOL INJ IV CX 12 FR PLAS TRANS SIST FECH X 1000 ML Ativo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
